--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487931_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487931_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.1822</v>
+        <v>5.0755</v>
       </c>
       <c r="E2" t="n">
-        <v>4.0027</v>
+        <v>3.9841</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1795</v>
+        <v>1.0915</v>
       </c>
       <c r="G2" t="n">
         <v>3.5113</v>
@@ -610,13 +610,13 @@
         <v>1.6649</v>
       </c>
       <c r="S2" t="n">
-        <v>0.749</v>
+        <v>0.6423</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3047</v>
+        <v>-0.3233</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0537</v>
+        <v>0.9656</v>
       </c>
       <c r="V2" t="n">
         <v>2.795</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Z. WILLIAMS</t>
+          <t>A. HERRERA DOMINGUEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.3986</v>
+        <v>4.5431</v>
       </c>
       <c r="E3" t="n">
-        <v>3.6182</v>
+        <v>4.0765</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7804</v>
+        <v>0.4666</v>
       </c>
       <c r="G3" t="n">
-        <v>4.2241</v>
+        <v>4.7104</v>
       </c>
       <c r="H3" t="n">
-        <v>2.5349</v>
+        <v>0.7548</v>
       </c>
       <c r="I3" t="n">
-        <v>1.6892</v>
+        <v>3.9556</v>
       </c>
       <c r="J3" t="n">
-        <v>4.7427</v>
+        <v>5.2045</v>
       </c>
       <c r="K3" t="n">
-        <v>3.4495</v>
+        <v>1.1469</v>
       </c>
       <c r="L3" t="n">
-        <v>1.2932</v>
+        <v>4.0576</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5185999999999999</v>
+        <v>-0.4941</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9145</v>
+        <v>-0.3921</v>
       </c>
       <c r="O3" t="n">
-        <v>0.396</v>
+        <v>-0.102</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.8731</v>
+        <v>-1.4568</v>
       </c>
       <c r="Q3" t="n">
         <v>-2.0812</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2081</v>
+        <v>0.6244</v>
       </c>
       <c r="S3" t="n">
-        <v>1.8176</v>
+        <v>0.122</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7268</v>
+        <v>-0.4443</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0909</v>
+        <v>0.5663</v>
       </c>
       <c r="V3" t="n">
-        <v>0.23</v>
+        <v>1.1675</v>
       </c>
       <c r="W3" t="n">
-        <v>0.23</v>
+        <v>1.3975</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. HERRERA DOMINGUEZ</t>
+          <t>V. ORLOV STURMAN MAURIN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.2202</v>
+        <v>3.7899</v>
       </c>
       <c r="E4" t="n">
-        <v>4.0765</v>
+        <v>1.6322</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1437</v>
+        <v>2.1576</v>
       </c>
       <c r="G4" t="n">
-        <v>4.7104</v>
+        <v>1.5458</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7548</v>
+        <v>-0.3091</v>
       </c>
       <c r="I4" t="n">
-        <v>3.9556</v>
+        <v>1.8549</v>
       </c>
       <c r="J4" t="n">
-        <v>5.2045</v>
+        <v>0.7785</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1469</v>
+        <v>0.034</v>
       </c>
       <c r="L4" t="n">
-        <v>4.0576</v>
+        <v>0.7446</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4941</v>
+        <v>0.7673</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3921</v>
+        <v>-0.3431</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.102</v>
+        <v>1.1104</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.4568</v>
+        <v>0.2081</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6244</v>
+        <v>0.2081</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2009</v>
+        <v>0.8683999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4443</v>
+        <v>-0.3138</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2434</v>
+        <v>1.1822</v>
       </c>
       <c r="V4" t="n">
         <v>1.1675</v>
       </c>
       <c r="W4" t="n">
-        <v>1.3975</v>
+        <v>1.1675</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>V. ORLOV STURMAN MAURIN</t>
+          <t>Z. WILLIAMS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.966</v>
+        <v>3.5884</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6322</v>
+        <v>3.1896</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3338</v>
+        <v>0.3988</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5458</v>
+        <v>4.2241</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3091</v>
+        <v>2.5349</v>
       </c>
       <c r="I5" t="n">
-        <v>1.8549</v>
+        <v>1.6892</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7785</v>
+        <v>4.7427</v>
       </c>
       <c r="K5" t="n">
-        <v>0.034</v>
+        <v>3.4495</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7446</v>
+        <v>1.2932</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7673</v>
+        <v>-0.5185999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3431</v>
+        <v>-0.9145</v>
       </c>
       <c r="O5" t="n">
-        <v>1.1104</v>
+        <v>0.396</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2081</v>
+        <v>-1.8731</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R5" t="n">
         <v>0.2081</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0446</v>
+        <v>1.0073</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3138</v>
+        <v>0.2981</v>
       </c>
       <c r="U5" t="n">
-        <v>1.3584</v>
+        <v>0.7092000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>1.1675</v>
+        <v>0.23</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1675</v>
+        <v>0.23</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4525</v>
+        <v>1.8765</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0575</v>
+        <v>1.188</v>
       </c>
       <c r="F6" t="n">
-        <v>0.395</v>
+        <v>0.6885</v>
       </c>
       <c r="G6" t="n">
         <v>-1.0537</v>
@@ -922,13 +922,13 @@
         <v>0.6244</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1305</v>
+        <v>0.5546</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.171</v>
+        <v>-0.0405</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3014</v>
+        <v>0.595</v>
       </c>
       <c r="V6" t="n">
         <v>1.7513</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9689</v>
+        <v>1.3026</v>
       </c>
       <c r="E7" t="n">
-        <v>0.588</v>
+        <v>0.5695</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3808</v>
+        <v>0.7331</v>
       </c>
       <c r="G7" t="n">
         <v>-2.0517</v>
@@ -1000,13 +1000,13 @@
         <v>1.2487</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2068</v>
+        <v>0.5405</v>
       </c>
       <c r="T7" t="n">
-        <v>0.152</v>
+        <v>0.1334</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0548</v>
+        <v>0.4071</v>
       </c>
       <c r="V7" t="n">
         <v>1.9813</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. CORREIA</t>
+          <t>A. MARIN ORTEGA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3931</v>
+        <v>0.1063</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5149</v>
+        <v>0.2189</v>
       </c>
       <c r="F8" t="n">
-        <v>0.908</v>
+        <v>-0.1125</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.5509</v>
+        <v>0.7185</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.55</v>
+        <v>0.7144</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.0009</v>
+        <v>0.0041</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7393999999999999</v>
+        <v>1.2738</v>
       </c>
       <c r="K8" t="n">
-        <v>0.034</v>
+        <v>1.2044</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7054</v>
+        <v>0.0694</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.2902</v>
+        <v>-0.5554</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5839</v>
+        <v>-0.4901</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.7063</v>
+        <v>-0.0653</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2081</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.4568</v>
+        <v>-1.2487</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6649</v>
+        <v>1.0406</v>
       </c>
       <c r="S8" t="n">
-        <v>1.1698</v>
+        <v>0.7635</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8234</v>
+        <v>-0.39</v>
       </c>
       <c r="U8" t="n">
-        <v>1.9932</v>
+        <v>1.1535</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5661</v>
+        <v>-1.1675</v>
       </c>
       <c r="W8" t="n">
-        <v>1.026</v>
+        <v>0.5838</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.4599</v>
+        <v>-1.7513</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. MARIN ORTEGA</t>
+          <t>S. CORREIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2063</v>
+        <v>-0.1173</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1117</v>
+        <v>0.0023</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3181</v>
+        <v>-0.1196</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7185</v>
+        <v>-1.5509</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7144</v>
+        <v>-0.55</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0041</v>
+        <v>-1.0009</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2738</v>
+        <v>0.7393999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>1.2044</v>
+        <v>0.034</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0694</v>
+        <v>0.7054</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5554</v>
+        <v>-2.2902</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4901</v>
+        <v>-0.5839</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0653</v>
+        <v>-1.7063</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.2081</v>
+        <v>0.2081</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.2487</v>
+        <v>-1.4568</v>
       </c>
       <c r="R9" t="n">
-        <v>1.0406</v>
+        <v>1.6649</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4508</v>
+        <v>0.6595</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4972</v>
+        <v>-0.3062</v>
       </c>
       <c r="U9" t="n">
-        <v>0.948</v>
+        <v>0.9656</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.1675</v>
+        <v>0.5661</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5838</v>
+        <v>1.026</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.7513</v>
+        <v>-0.4599</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2104</v>
+        <v>-0.181</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2104</v>
+        <v>-0.181</v>
       </c>
       <c r="G10" t="n">
         <v>0.1429</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1233</v>
+        <v>-0.0939</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1233</v>
+        <v>-0.0939</v>
       </c>
       <c r="V10" t="n">
         <v>-0.23</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.9363</v>
+        <v>-0.7536</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.8753</v>
+        <v>-2.8101</v>
       </c>
       <c r="F11" t="n">
-        <v>1.9391</v>
+        <v>2.0565</v>
       </c>
       <c r="G11" t="n">
         <v>0.1037</v>
@@ -1312,13 +1312,13 @@
         <v>0.2081</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2075</v>
+        <v>-0.0248</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5219</v>
+        <v>-0.4567</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3145</v>
+        <v>0.4319</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.658</v>
+        <v>-1.4627</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.0184</v>
+        <v>0.0888</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.6396</v>
+        <v>-1.5515</v>
       </c>
       <c r="G12" t="n">
         <v>-1.3745</v>
@@ -1390,13 +1390,13 @@
         <v>0.2081</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4104</v>
+        <v>-0.2151</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3262</v>
+        <v>-0.2191</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0842</v>
+        <v>0.0039</v>
       </c>
       <c r="V12" t="n">
         <v>1.1675</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.2386</v>
+        <v>-3.4572</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.4239</v>
+        <v>-2.9067</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.8147</v>
+        <v>-0.5505</v>
       </c>
       <c r="G13" t="n">
         <v>-4.1291</v>
@@ -1468,13 +1468,13 @@
         <v>1.6649</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7744</v>
+        <v>0.007</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0191</v>
+        <v>-0.5019</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2447</v>
+        <v>0.5089</v>
       </c>
       <c r="V13" t="n">
         <v>-0.5838</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>13.3319</v>
+        <v>14.3105</v>
       </c>
       <c r="E14" t="n">
-        <v>8.254300000000001</v>
+        <v>9.2331</v>
       </c>
       <c r="F14" t="n">
-        <v>5.077500000000001</v>
+        <v>5.077499999999999</v>
       </c>
       <c r="G14" t="n">
         <v>4.7968</v>
       </c>
       <c r="H14" t="n">
-        <v>3.347500000000001</v>
+        <v>3.3475</v>
       </c>
       <c r="I14" t="n">
         <v>1.449300000000001</v>
@@ -1528,7 +1528,7 @@
         <v>4.4291</v>
       </c>
       <c r="M14" t="n">
-        <v>-7.614599999999999</v>
+        <v>-7.614600000000001</v>
       </c>
       <c r="N14" t="n">
         <v>-4.634999999999999</v>
@@ -1546,13 +1546,13 @@
         <v>9.3652</v>
       </c>
       <c r="S14" t="n">
-        <v>3.8526</v>
+        <v>4.831300000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.5428</v>
+        <v>-2.5643</v>
       </c>
       <c r="U14" t="n">
-        <v>7.3955</v>
+        <v>7.3953</v>
       </c>
       <c r="V14" t="n">
         <v>8.844899999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.381</v>
+        <v>2.2383</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9025</v>
+        <v>2.3311</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5215</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="G15" t="n">
         <v>2.9968</v>
@@ -1624,13 +1624,13 @@
         <v>1.8731</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.1711</v>
+        <v>-0.3138</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.4882</v>
+        <v>-1.0596</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3171</v>
+        <v>0.7458</v>
       </c>
       <c r="V15" t="n">
         <v>-1.2772</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. HAYES</t>
+          <t>J. CERA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.508</v>
+        <v>0.9868</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7835</v>
+        <v>1.1119</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2755</v>
+        <v>-0.1251</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.5294</v>
+        <v>1.0988</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.5865</v>
+        <v>-0.3731</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0572</v>
+        <v>1.472</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9119</v>
+        <v>3.1238</v>
       </c>
       <c r="K16" t="n">
-        <v>0.7159</v>
+        <v>0.8355</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1959</v>
+        <v>2.2884</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.4412</v>
+        <v>-2.025</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.3025</v>
+        <v>-1.2086</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1388</v>
+        <v>-0.8164</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4162</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4568</v>
+        <v>1.6649</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2531</v>
+        <v>-1.0897</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8391</v>
+        <v>-1.5582</v>
       </c>
       <c r="U16" t="n">
-        <v>1.0922</v>
+        <v>0.4685</v>
       </c>
       <c r="V16" t="n">
-        <v>0.368</v>
+        <v>1.3939</v>
       </c>
       <c r="W16" t="n">
-        <v>1.7513</v>
+        <v>1.6275</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.3833</v>
+        <v>-0.2335</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. CERA RODRIGUEZ</t>
+          <t>R. HAYES</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.08989999999999999</v>
+        <v>-0.0039</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7905</v>
+        <v>0.5692</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7005</v>
+        <v>-0.5731000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>1.0988</v>
+        <v>-0.5294</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3731</v>
+        <v>-0.5865</v>
       </c>
       <c r="I17" t="n">
-        <v>1.472</v>
+        <v>0.0572</v>
       </c>
       <c r="J17" t="n">
-        <v>3.1238</v>
+        <v>0.9119</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8355</v>
+        <v>0.7159</v>
       </c>
       <c r="L17" t="n">
-        <v>2.2884</v>
+        <v>0.1959</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.025</v>
+        <v>-1.4412</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.2086</v>
+        <v>-1.3025</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.8164</v>
+        <v>-0.1388</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.4162</v>
+        <v>0.4162</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6649</v>
+        <v>1.4568</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.9866</v>
+        <v>-0.2587</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.8797</v>
+        <v>-1.0534</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.107</v>
+        <v>0.7947</v>
       </c>
       <c r="V17" t="n">
-        <v>1.3939</v>
+        <v>0.368</v>
       </c>
       <c r="W17" t="n">
-        <v>1.6275</v>
+        <v>1.7513</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2335</v>
+        <v>-1.3833</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2148</v>
+        <v>-0.9608</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0509</v>
+        <v>0.1581</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2657</v>
+        <v>-1.1189</v>
       </c>
       <c r="G18" t="n">
         <v>0.4263</v>
@@ -1858,13 +1858,13 @@
         <v>0.2081</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0979</v>
+        <v>0.1561</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1957</v>
+        <v>-0.0886</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0979</v>
+        <v>0.2447</v>
       </c>
       <c r="V18" t="n">
         <v>-1.7513</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. ROMERO SANCHEZ</t>
+          <t>R. BLAK MOLLER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4503</v>
+        <v>-1.0702</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3855</v>
+        <v>-1.7646</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.8359</v>
+        <v>0.6944</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1345</v>
+        <v>-1.3472</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.3517</v>
+        <v>0.3584</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2173</v>
+        <v>-1.7055</v>
       </c>
       <c r="J19" t="n">
-        <v>1.7803</v>
+        <v>-1.2736</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.0044</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>1.7847</v>
+        <v>-1.3504</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.9147</v>
+        <v>-0.0735</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.3473</v>
+        <v>0.2816</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5674</v>
+        <v>-0.3551</v>
       </c>
       <c r="P19" t="n">
-        <v>1.6649</v>
+        <v>0.6244</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6649</v>
+        <v>0.6244</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.062</v>
+        <v>0.1125</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3948</v>
+        <v>-0.491</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3327</v>
+        <v>0.6035</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.9188</v>
+        <v>-0.4599</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.9188</v>
+        <v>-0.4599</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. BLAK MOLLER</t>
+          <t>S. ROMERO SANCHEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6583</v>
+        <v>-1.352</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.9789</v>
+        <v>1.2784</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3206</v>
+        <v>-2.6303</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.3472</v>
+        <v>-0.1345</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3584</v>
+        <v>-1.3517</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.7055</v>
+        <v>1.2173</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.2736</v>
+        <v>1.7803</v>
       </c>
       <c r="K20" t="n">
-        <v>0.07679999999999999</v>
+        <v>-0.0044</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.3504</v>
+        <v>1.7847</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0735</v>
+        <v>-1.9147</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2816</v>
+        <v>-1.3473</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3551</v>
+        <v>-0.5674</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6244</v>
+        <v>1.6649</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6244</v>
+        <v>1.6649</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4756</v>
+        <v>0.0363</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7053</v>
+        <v>-0.5019</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2297</v>
+        <v>0.5383</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.4599</v>
+        <v>-2.9188</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.4599</v>
+        <v>-2.9188</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0649</v>
+        <v>-2.1109</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.781</v>
+        <v>-1.9954</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2839</v>
+        <v>-0.1156</v>
       </c>
       <c r="G21" t="n">
         <v>-0.841</v>
@@ -2092,13 +2092,13 @@
         <v>1.2487</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5461</v>
+        <v>0.5001</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0619</v>
+        <v>-0.1524</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4841</v>
+        <v>0.6524</v>
       </c>
       <c r="V21" t="n">
         <v>-0.9376</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. MORALES ROS</t>
+          <t>N. OKEKE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.824</v>
+        <v>-2.6038</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.7876</v>
+        <v>-2.6369</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.0364</v>
+        <v>0.0331</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.4022</v>
+        <v>-1.0304</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.4626</v>
+        <v>0.9510999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0604</v>
+        <v>-1.9815</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.5853</v>
+        <v>1.2478</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.3926</v>
+        <v>2.1639</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.1927</v>
+        <v>-0.9161</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.8169</v>
+        <v>-2.2782</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.07</v>
+        <v>-1.2127</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2531</v>
+        <v>-1.0654</v>
       </c>
       <c r="P22" t="n">
-        <v>1.6649</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-3.1218</v>
       </c>
       <c r="R22" t="n">
-        <v>1.6649</v>
+        <v>2.7055</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2258</v>
+        <v>0.0138</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2023</v>
+        <v>-0.9929</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0235</v>
+        <v>1.0067</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.861</v>
+        <v>-1.1711</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.861</v>
+        <v>-1.401</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>N. OKEKE</t>
+          <t>A. MORALES ROS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.9047</v>
+        <v>-3.0892</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.7441</v>
+        <v>-1.4306</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1607</v>
+        <v>-1.6586</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.0304</v>
+        <v>-2.4022</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9510999999999999</v>
+        <v>-2.4626</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.9815</v>
+        <v>0.0604</v>
       </c>
       <c r="J23" t="n">
-        <v>1.2478</v>
+        <v>-0.5853</v>
       </c>
       <c r="K23" t="n">
-        <v>2.1639</v>
+        <v>-0.3926</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.9161</v>
+        <v>-0.1927</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.2782</v>
+        <v>-1.8169</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.2127</v>
+        <v>-2.07</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.0654</v>
+        <v>0.2531</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.4162</v>
+        <v>1.6649</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.1218</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.7055</v>
+        <v>1.6649</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2871</v>
+        <v>-0.491</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1</v>
+        <v>-0.8453000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.3543</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.1711</v>
+        <v>-1.861</v>
       </c>
       <c r="W23" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.401</v>
+        <v>-1.861</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.1938</v>
+        <v>-3.2232</v>
       </c>
       <c r="E24" t="n">
         <v>-2.6988</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.495</v>
+        <v>-0.5244</v>
       </c>
       <c r="G24" t="n">
         <v>-3.0343</v>
@@ -2326,13 +2326,13 @@
         <v>0.4162</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3458</v>
+        <v>-0.3751</v>
       </c>
       <c r="T24" t="n">
         <v>-0.6524</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3066</v>
+        <v>0.2773</v>
       </c>
       <c r="V24" t="n">
         <v>-0.23</v>
@@ -2359,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-13.3319</v>
+        <v>-11.1889</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.0775</v>
+        <v>-5.077599999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-8.2545</v>
+        <v>-6.1113</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.797099999999999</v>
+        <v>-4.7971</v>
       </c>
       <c r="H25" t="n">
         <v>-3.347399999999999</v>
@@ -2383,7 +2383,7 @@
         <v>4.6351</v>
       </c>
       <c r="L25" t="n">
-        <v>2.979699999999999</v>
+        <v>2.9797</v>
       </c>
       <c r="M25" t="n">
         <v>-12.4115</v>
@@ -2392,7 +2392,7 @@
         <v>-7.982599999999999</v>
       </c>
       <c r="O25" t="n">
-        <v>-4.428900000000001</v>
+        <v>-4.4289</v>
       </c>
       <c r="P25" t="n">
         <v>4.1623</v>
@@ -2404,16 +2404,16 @@
         <v>13.5275</v>
       </c>
       <c r="S25" t="n">
-        <v>-3.8527</v>
+        <v>-1.7095</v>
       </c>
       <c r="T25" t="n">
-        <v>-7.3956</v>
+        <v>-7.3957</v>
       </c>
       <c r="U25" t="n">
-        <v>3.542799999999999</v>
+        <v>5.686200000000001</v>
       </c>
       <c r="V25" t="n">
-        <v>-8.845000000000002</v>
+        <v>-8.845000000000001</v>
       </c>
       <c r="W25" t="n">
         <v>4.0688</v>
